--- a/小野町_引継ぎ_整理済/12_進捗管理/小野町_計画策定業務_進捗管理表_20260805.xlsx
+++ b/小野町_引継ぎ_整理済/12_進捗管理/小野町_計画策定業務_進捗管理表_20260805.xlsx
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -670,7 +670,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>成果品①は第3版、③は第3版を作成済み。②は認定者推計の確定が前提</t>
+          <t>成果品①は第4版、③は第3版を作成済み。②は認定者推計の確定が前提</t>
         </is>
       </c>
     </row>
@@ -786,10 +786,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>16</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr"/>
@@ -925,61 +925,75 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>令和7年度調査（ニーズ調査・在宅介護実態調査）は未受領である（8月5日送付分は地域福祉計画の本編・概要版のみ）。**クロス集計は単純集計からは作成できず、個票データが必須である。**クロス集計設計書（ニーズ調査13件・在宅介護実態調査12件）を作成済みで、個票受領後ただちに実行できる状態にある。</t>
+          <t>令和7年度調査の結果報告書を受領し、集計データを整理した。**在宅の要介護認定者の42.1％がサービスを利用しておらず、その理由の92.9％が需要側の要因（状態ではない46.8％、本人の希望なし29.2％、家族が介護16.9％）で、供給制約は0.6％であった。**これにより第10期の施策方向を、供給確保から認定運用の確認・利用意向への働きかけ・レスパイトへ組み替える。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>障がい計画は、委託仕様が定める関係者団体等ヒアリングが未着手であり、調査票も児童用に本文欠落が残る。工程上、8月中の調査票確定が必要。</t>
+          <t>**通いの場は調査で週1回以上の参加が5.5％（約190人規模）との回答があり、見える化システムの0か所と整合しない。**介護予防の評価を保留し、町の事業実績による確認を求めている。リスク10項目は8項目で改善したが、回収率が77.7％→67.9％へ低下している。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
+          <t>クロス集計は設計25件のうち4件が報告書に掲載済み、17件が個票を要し、4件は該当する設問が存在しない。個票の受領が次の律速となる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>障がい計画は、委託仕様が定める関係者団体等ヒアリングが未着手であり、調査票も児童用に本文欠落が残る。工程上、8月中の調査票確定が必要。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
           <t>委託仕様書の工程（障がい：調査は7月まで、骨子案9月、骨子案検討10月）から3〜4か月遅延している。工程変更について町との協議・記録化が必要（仕様書8①・11④）。</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>■ 直近のマイルストーン</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>令和8年8月19日　小野町自立支援協議会（第1回）　※資料第3版を作成済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>令和8年8〜9月　　高齢者福祉サービス推進協議会：第9期評価・調査結果　※資料作成済み、開催日未定</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>令和8年8月中　　障がい者ニーズ調査の調査票確定（児童用の本文復元が前提）</t>
+          <t>令和8年8月19日　小野町自立支援協議会（第1回）　※資料第3版を作成済み</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>令和8年9〜10月　障がい者ニーズ調査の発送・回収、関係者団体等ヒアリング</t>
+          <t>令和8年8〜9月　　高齢者福祉サービス推進協議会：第9期評価・調査結果　※資料作成済み、開催日未定</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
+        <is>
+          <t>令和8年8月中　　障がい者ニーズ調査の調査票確定（児童用の本文復元が前提）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>令和8年9〜10月　障がい者ニーズ調査の発送・回収、関係者団体等ヒアリング</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>令和8年12月頃　 自立支援協議会（第2回）：調査結果・骨子案・見込量の考え方</t>
         </is>
@@ -1253,7 +1267,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>**アンケートは未受領（8月5日送付分は地域福祉計画のみ）。** クロス集計設計書（24件・8シート）を作成済み。協議会資料 第2部に前回調査（R4・R5）の値を比較基準として整理済み</t>
+          <t>**調査結果報告書（令和8年3月・104頁）を受領し集計データを整理済み。** リスク10項目の前回対比、未利用理由、通いの場、介護者の状況を確定。報告書の不整合2件（回収数319とn=366、まとめの転記誤り）を検出</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -1603,7 +1617,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>第3版作成済み（8章・表40・約26,000字）。見える化データに基づく分析は完了。第9期計画との対比、施策体系との対応、町の公式統計による認定者数8年系列まで整理済み</t>
+          <t>第4版作成済み（8章・表42・約27,500字）。第9期計画との対比、施策体系との対応、認定者数8年系列、令和7年度調査による未利用理由・通いの場の検証まで整理済み</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -2777,7 +2791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3372,7 +3386,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>令和7年度 ニーズ調査・在宅介護実態調査の**個票データ**</t>
+          <t>令和7年度 調査結果報告書（令和8年3月・104頁）</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
@@ -3380,19 +3394,19 @@
           <t>町</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>要対応</t>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>**8月5日の送付分は地域福祉計画（本編・概要版）のみでアンケートは未着。**クロス集計は単純集計からは作成できず個票が必須。クロス集計設計書（24件）を作成済みで、受領即実行できる状態</t>
+          <t>**単純集計とリスク分析（年齢階層別・男女別・認定状況別）を取得。**設計25件のうち4件が掲載済み、17件が個票を要し、4件は設問が存在しない</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3418,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>令和7年度調査の調査票・配布数・回収数・実施時期</t>
+          <t>令和7年度調査の**個票データ**</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
@@ -3412,9 +3426,9 @@
           <t>町</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
@@ -3424,7 +3438,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>計画書第2章1(1)の記載と、前回調査との設問の異同の確認に必要</t>
+          <t>要介護度別・世帯構成別のクロス集計17件に必要。地区情報の有無も要確認（層化抽出に居住地区を用いている）</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3450,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>在宅介護実態調査の**配布方法**（ケアマネジャー経由か否か）</t>
+          <t>令和7年度調査の調査票・配布数・回収数・実施時期</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
@@ -3456,7 +3470,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>**ケアマネジャー経由の場合、サービス未利用者が構造的に対象外となり、認定と利用のギャップを検証できない。**補足調査の要否判断に直結</t>
+          <t>計画書第2章1(1)の記載と、前回調査との設問の異同の確認に必要</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3482,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高と取崩方針</t>
+          <t>在宅介護実態調査の**配布方法**（ケアマネジャー経由か否か）</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
@@ -3488,7 +3502,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>保険料算定に必須</t>
+          <t>**ケアマネジャー経由の場合、サービス未利用者が構造的に対象外となり、認定と利用のギャップを検証できない。**補足調査の要否判断に直結</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3514,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>所得段階別第1号被保険者数</t>
+          <t>介護給付費準備基金の残高と取崩方針</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
@@ -3520,7 +3534,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>保険料算定に必須</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3546,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>地域支援事業費の実績と事業別内訳</t>
+          <t>所得段階別第1号被保険者数</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -3564,7 +3578,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>総合事業・通いの場の事業実績（令和3〜7年度）</t>
+          <t>地域支援事業費の実績と事業別内訳</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
@@ -3584,7 +3598,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>見える化に令和3年度以降がないため代替が必要</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3610,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>事業所別定員・稼働率・町内外利用・待機・休廃止</t>
+          <t>総合事業・通いの場の事業実績（令和3〜7年度）</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
@@ -3616,7 +3630,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>供給制約の確認</t>
+          <t>見える化に令和3年度以降がないため代替が必要</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3642,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>居宅介護支援事業所の担当件数・受付状況</t>
+          <t>事業所別定員・稼働率・町内外利用・待機・休廃止</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
@@ -3648,7 +3662,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>事業所5→3の減少と在宅利用低下の関係</t>
+          <t>供給制約の確認</t>
         </is>
       </c>
     </row>
@@ -3660,12 +3674,12 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>認知症施策の実績（研修、初期集中支援チーム等）</t>
+          <t>居宅介護支援事業所の担当件数・受付状況</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>町・県</t>
+          <t>町</t>
         </is>
       </c>
       <c r="D28" s="16" t="inlineStr">
@@ -3680,7 +3694,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>見える化では把握できない</t>
+          <t>事業所5→3の減少と在宅利用低下の関係</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3706,12 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>障がい：令和6〜8年度 サービス別実績、支給決定量、町内外事業所別利用</t>
+          <t>認知症施策の実績（研修、初期集中支援チーム等）</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>町・県</t>
         </is>
       </c>
       <c r="D29" s="16" t="inlineStr">
@@ -3712,7 +3726,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>見込量算定に必須</t>
+          <t>見える化では把握できない</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3738,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>障がい：セルフプラン件数、相談支援専門員数</t>
+          <t>障がい：令和6〜8年度 サービス別実績、支給決定量、町内外事業所別利用</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
@@ -3744,7 +3758,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>国の新規成果目標「望まないセルフプランゼロ」の起点</t>
+          <t>見込量算定に必須</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3770,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>障がい：特別支援学校卒業予定者、医療的ケア児の状況</t>
+          <t>障がい：セルフプラン件数、相談支援専門員数</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
@@ -3776,24 +3790,24 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>18歳移行の見込量</t>
+          <t>国の新規成果目標「望まないセルフプランゼロ」の起点</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>町資料</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>★0727版アンケート調査票（一般用・児童用）</t>
+          <t>障がい：特別支援学校卒業予定者、医療的ケア児の状況</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>町・他メンバー</t>
+          <t>町</t>
         </is>
       </c>
       <c r="D32" s="16" t="inlineStr">
@@ -3808,7 +3822,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>本文復元の対象ファイル。手元にない</t>
+          <t>18歳移行の見込量</t>
         </is>
       </c>
     </row>
@@ -3820,25 +3834,57 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
+          <t>★0727版アンケート調査票（一般用・児童用）</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>町・他メンバー</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>本文復元の対象ファイル。手元にない</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
           <t>打合せ記録（契約後）</t>
         </is>
       </c>
-      <c r="C33" s="13" t="inlineStr">
+      <c r="C34" s="13" t="inlineStr">
         <is>
           <t>受託者作成・町確認</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>仕様書8①により受託者が作成し相互確認する義務</t>
         </is>

--- a/小野町_引継ぎ_整理済/12_進捗管理/小野町_計画策定業務_進捗管理表_20260805.xlsx
+++ b/小野町_引継ぎ_整理済/12_進捗管理/小野町_計画策定業務_進捗管理表_20260805.xlsx
@@ -939,7 +939,7 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>クロス集計は設計25件のうち4件が報告書に掲載済み、17件が個票を要し、4件は該当する設問が存在しない。個票の受領が次の律速となる。</t>
+          <t>クロス集計は設計25件のうち4件が報告書に掲載済み、17件が個票を要し、4件は該当する設問が存在しない。個票の受領が次の律速となる。ただし施策の方向は単純集計の段階で判断できる水準に達しており、集計結果・分析報告書として取りまとめた。</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>**調査結果報告書（令和8年3月・104頁）を受領し集計データを整理済み。** リスク10項目の前回対比、未利用理由、通いの場、介護者の状況を確定。報告書の不整合2件（回収数319とn=366、まとめの転記誤り）を検出</t>
+          <t>**集計結果・分析報告書（7章・表72・約27,800字）を作成済み。** 単純集計、リスク分析（年齢/男女/認定状況別）、前回対比、8つの分析、第9期課題への到達状況、第10期への示唆まで整理</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>**単純集計とリスク分析（年齢階層別・男女別・認定状況別）を取得。**設計25件のうち4件が掲載済み、17件が個票を要し、4件は設問が存在しない</t>
+          <t>**単純集計とリスク分析（年齢階層別・男女別・認定状況別）を取得。**集計結果・分析報告書として取りまとめ済み。設計25件のうち4件が掲載済み、17件が個票を要し、4件は設問が存在しない</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/12_進捗管理/小野町_計画策定業務_進捗管理表_20260805.xlsx
+++ b/小野町_引継ぎ_整理済/12_進捗管理/小野町_計画策定業務_進捗管理表_20260805.xlsx
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -617,7 +617,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
@@ -626,11 +626,11 @@
         <v>3</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -652,7 +652,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -661,16 +661,16 @@
         <v>0</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>成果品①は第4版、③は第3版を作成済み。②は認定者推計の確定が前提</t>
+          <t>成果品①は第4版、③は第3版、④は第2版を作成済み。②は認定者推計の確定が前提</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
         <v>18</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>8</v>
@@ -871,11 +871,11 @@
         <v>4</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr"/>
@@ -939,61 +939,68 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>クロス集計は設計25件のうち4件が報告書に掲載済み、17件が個票を要し、4件は該当する設問が存在しない。個票の受領が次の律速となる。ただし施策の方向は単純集計の段階で判断できる水準に達しており、集計結果・分析報告書として取りまとめた。</t>
+          <t>調査結果を反映し、高齢者計画の素案を第2版に全面改訂した。第9期の5章構成・3基本目標を継承し、地域福祉計画への移管・連携を整理した結果、施策は14から12に再編された。12施策すべてに現状と課題・施策の方向・主な事業・成果指標（案）を記載している。サービス見込量と保険料は認定者数の確定後に算定する。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>障がい計画は、委託仕様が定める関係者団体等ヒアリングが未着手であり、調査票も児童用に本文欠落が残る。工程上、8月中の調査票確定が必要。</t>
+          <t>クロス集計は設計25件のうち4件が報告書に掲載済み、17件が個票を要し、4件は該当する設問が存在しない。個票の受領が次の律速となる。ただし施策の方向は単純集計の段階で判断できる水準に達しており、集計結果・分析報告書として取りまとめた。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
+          <t>障がい計画は、委託仕様が定める関係者団体等ヒアリングが未着手であり、調査票も児童用に本文欠落が残る。工程上、8月中の調査票確定が必要。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
           <t>委託仕様書の工程（障がい：調査は7月まで、骨子案9月、骨子案検討10月）から3〜4か月遅延している。工程変更について町との協議・記録化が必要（仕様書8①・11④）。</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>■ 直近のマイルストーン</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>令和8年8月19日　小野町自立支援協議会（第1回）　※資料第3版を作成済み</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>令和8年8〜9月　　高齢者福祉サービス推進協議会：第9期評価・調査結果　※資料作成済み、開催日未定</t>
+          <t>令和8年8月19日　小野町自立支援協議会（第1回）　※資料第3版を作成済み</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>令和8年8月中　　障がい者ニーズ調査の調査票確定（児童用の本文復元が前提）</t>
+          <t>令和8年8〜9月　　高齢者福祉サービス推進協議会：第9期評価・調査結果　※資料作成済み、開催日未定</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>令和8年9〜10月　障がい者ニーズ調査の発送・回収、関係者団体等ヒアリング</t>
+          <t>令和8年8月中　　障がい者ニーズ調査の調査票確定（児童用の本文復元が前提）</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
+        <is>
+          <t>令和8年9〜10月　障がい者ニーズ調査の発送・回収、関係者団体等ヒアリング</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>令和8年12月頃　 自立支援協議会（第2回）：調査結果・骨子案・見込量の考え方</t>
         </is>
@@ -1445,24 +1452,24 @@
           <t>骨子案を踏まえた計画素案</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>引継ぎ資料に拡充版あり（数値未反映）</t>
+          <t>**高齢者計画 素案 第2版を作成済み（5章＋資料編・表64・約29,600字）。**第9期の5章構成・3基本目標を継承し12施策すべてに現状と課題・施策の方向・主な事業・成果指標（案）を記載。令和7年度調査結果を反映</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>骨子案の合意後に着手</t>
+          <t>認定者数の確定によりサービス見込量・保険料を算定し確定稿とする。協議会に諮る</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>骨子案の合意</t>
+          <t>認定者数の確定</t>
         </is>
       </c>
     </row>
@@ -1706,19 +1713,19 @@
           <t>データCD-R1部＋冊子（簡易製本）3部</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>引継ぎ資料に拡充版あり（町資料・実績反映前のたたき台）</t>
+          <t>**第2版作成済み（5章＋資料編・表64・約29,600字）。**調査結果を反映し、12施策の本文と成果指標（案）まで記載。【データ待ち】153箇所</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>骨子案の合意、実績データ、調査結果</t>
+          <t>認定者数の確定（見込量・保険料）、決算、事業実績、協議会での合意</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/12_進捗管理/小野町_計画策定業務_進捗管理表_20260805.xlsx
+++ b/小野町_引継ぎ_整理済/12_進捗管理/小野町_計画策定業務_進捗管理表_20260805.xlsx
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -670,7 +670,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>成果品①は第4版、③は第3版、④は第2版を作成済み。②は認定者推計の確定が前提</t>
+          <t>成果品①は第5版、③は第3版、④は第2版。②は令和8年3月末の認定者数の確認が前提</t>
         </is>
       </c>
     </row>
@@ -786,16 +786,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0</v>
@@ -805,12 +805,12 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>見える化は取得完了。第9期・第3期地域福祉計画から認定者数8年系列を取得。アンケート個票と令和6・7年度決算が未受領</t>
+          <t>見える化は取得完了（認定者数20期系列を含む）。アンケート個票と令和6・7年度決算が未受領</t>
         </is>
       </c>
     </row>
@@ -856,16 +856,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>18</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>4</v>
@@ -918,89 +918,96 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>第9期計画及び第3期地域福祉計画に掲載された介護保険事業状況報告により、平成30年から令和7年までの要介護度別認定者数（8年連続系列）を取得した。700人から953人へ36.1％増加し減少年はなく、見える化システムの令和8年3月末の値（783人・22.7％）が異常である根拠が5点となった。ただし令和8年3月末の実数と年度末基準の系列は引き続き未確認である。</t>
+          <t>見える化システムから認定者数の5系列（B3a〜B3e）を取得し、**平成19年3月末から令和8年3月末までの20期分について、年度末基準・要介護度別・年齢階層別の系列が確定した。**これにより計画素案の第2章3(1)及び第2章6の基礎データが揃った。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>令和7年度調査の結果報告書を受領し、集計データを整理した。**在宅の要介護認定者の42.1％がサービスを利用しておらず、その理由の92.9％が需要側の要因（状態ではない46.8％、本人の希望なし29.2％、家族が介護16.9％）で、供給制約は0.6％であった。**これにより第10期の施策方向を、供給確保から認定運用の確認・利用意向への働きかけ・レスパイトへ組み替える。</t>
+          <t>20期の系列で増減が突出しているのは2点のみである。令和2年度の＋107人（コロナに伴う認定有効期間の延長特例の時期と一致）と、令和7年度の▲152人である。**後者は減少の77.0％が85歳以上に集中しており、85歳以上の中でも重度ほど減少幅が大きい単調なパターンが現れる。**町の認定台帳による確認を要するが、確認の焦点は①85歳以上の異動の内訳、②認定有効期間の運用、の2点に絞られた。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>**通いの場は調査で週1回以上の参加が5.5％（約190人規模）との回答があり、見える化システムの0か所と整合しない。**介護予防の評価を保留し、町の事業実績による確認を求めている。リスク10項目は8項目で改善したが、回収率が77.7％→67.9％へ低下している。</t>
+          <t>令和7年度調査の結果報告書を受領し、集計データを整理した。**在宅の要介護認定者の42.1％がサービスを利用しておらず、その理由の92.9％が需要側の要因（状態ではない46.8％、本人の希望なし29.2％、家族が介護16.9％）で、供給制約は0.6％であった。**これにより第10期の施策方向を、供給確保から認定運用の確認・利用意向への働きかけ・レスパイトへ組み替える。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>調査結果を反映し、高齢者計画の素案を第2版に全面改訂した。第9期の5章構成・3基本目標を継承し、地域福祉計画への移管・連携を整理した結果、施策は14から12に再編された。12施策すべてに現状と課題・施策の方向・主な事業・成果指標（案）を記載している。サービス見込量と保険料は認定者数の確定後に算定する。</t>
+          <t>**通いの場は調査で週1回以上の参加が5.5％（約190人規模）との回答があり、見える化システムの0か所と整合しない。**介護予防の評価を保留し、町の事業実績による確認を求めている。リスク10項目は8項目で改善したが、回収率が77.7％→67.9％へ低下している。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>クロス集計は設計25件のうち4件が報告書に掲載済み、17件が個票を要し、4件は該当する設問が存在しない。個票の受領が次の律速となる。ただし施策の方向は単純集計の段階で判断できる水準に達しており、集計結果・分析報告書として取りまとめた。</t>
+          <t>調査結果を反映し、高齢者計画の素案を第2版に全面改訂した。第9期の5章構成・3基本目標を継承し、地域福祉計画への移管・連携を整理した結果、施策は14から12に再編された。12施策すべてに現状と課題・施策の方向・主な事業・成果指標（案）を記載している。サービス見込量と保険料は認定者数の確定後に算定する。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>障がい計画は、委託仕様が定める関係者団体等ヒアリングが未着手であり、調査票も児童用に本文欠落が残る。工程上、8月中の調査票確定が必要。</t>
+          <t>クロス集計は設計25件のうち4件が報告書に掲載済み、17件が個票を要し、4件は該当する設問が存在しない。個票の受領が次の律速となる。ただし施策の方向は単純集計の段階で判断できる水準に達しており、集計結果・分析報告書として取りまとめた。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
+          <t>障がい計画は、委託仕様が定める関係者団体等ヒアリングが未着手であり、調査票も児童用に本文欠落が残る。工程上、8月中の調査票確定が必要。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
           <t>委託仕様書の工程（障がい：調査は7月まで、骨子案9月、骨子案検討10月）から3〜4か月遅延している。工程変更について町との協議・記録化が必要（仕様書8①・11④）。</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>■ 直近のマイルストーン</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>令和8年8月19日　小野町自立支援協議会（第1回）　※資料第3版を作成済み</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>令和8年8〜9月　　高齢者福祉サービス推進協議会：第9期評価・調査結果　※資料作成済み、開催日未定</t>
+          <t>令和8年8月19日　小野町自立支援協議会（第1回）　※資料第3版を作成済み</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>令和8年8月中　　障がい者ニーズ調査の調査票確定（児童用の本文復元が前提）</t>
+          <t>令和8年8〜9月　　高齢者福祉サービス推進協議会：第9期評価・調査結果　※資料作成済み、開催日未定</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>令和8年9〜10月　障がい者ニーズ調査の発送・回収、関係者団体等ヒアリング</t>
+          <t>令和8年8月中　　障がい者ニーズ調査の調査票確定（児童用の本文復元が前提）</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
+        <is>
+          <t>令和8年9〜10月　障がい者ニーズ調査の発送・回収、関係者団体等ヒアリング</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>令和8年12月頃　 自立支援協議会（第2回）：調査結果・骨子案・見込量の考え方</t>
         </is>
@@ -1237,7 +1244,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>介護保険給付費等分析結果報告書 第3版（8章・表40）。第7章7に第9期の見込みとの対比、第2章2に町の公式統計による8年連続系列（H30 700人→R7 953人）を追加</t>
+          <t>介護保険給付費等分析結果報告書 第5版（8章・表44）。第2章に年度末基準20期の系列と年齢階層別分解、認定有効期間の運用に関する検討を追加</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -1624,7 +1631,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>第4版作成済み（8章・表42・約27,500字）。第9期計画との対比、施策体系との対応、認定者数8年系列、令和7年度調査による未利用理由・通いの場の検証まで整理済み</t>
+          <t>第5版作成済み（8章・表44・約29,500字）。第9期計画との対比、施策体系との対応、認定者数20期系列と年齢階層別分解、令和7年度調査による検証まで整理済み</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -2798,7 +2805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3265,7 +3272,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>令和8年3月末（令和7年度末）の認定者数（要介護度別）の実数</t>
+          <t>令和8年3月末の認定者数の**確認**（見える化の792人が正しいか）</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
@@ -3273,9 +3280,9 @@
           <t>町</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
@@ -3285,7 +3292,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>最優先。公式統計は令和7年7月31日まで。以降が未確認</t>
+          <t>**最優先。20期の系列で唯一の大幅減（▲152人）。減少の77.0％が85歳以上に集中**</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3304,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>令和3〜7年度 各年度末（3月末）の認定者数（要介護度別・年齢階層別）</t>
+          <t>85歳以上の認定者の令和7年度中の異動の内訳</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
@@ -3317,7 +3324,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>公式統計は10月1日基準。年度末基準の系列が認定者推計に必要</t>
+          <t>死亡・転出・非該当・更新未申請の別。減少の要因特定</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3336,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>認定審査・更新認定の運用変更の有無</t>
+          <t>認定有効期間の延長特例の適用件数と令和7年度の更新認定の状況</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
@@ -3349,39 +3356,39 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>**令和2年度の＋107人はコロナ特例（令和2年2月〜）の時期と一致。令和7年度の一斉満了の可能性を検証**</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>町資料</t>
+          <t>見える化</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>令和3〜8年度 サービス別給付費・利用者数</t>
+          <t>認定者数 年度末基準（B3a〜B3e／5系列）</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>町</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>見える化システム</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>見える化との突合</t>
+          <t>**平成19年3月末〜令和8年3月末の20期。要介護度別・年齢階層別（65〜74／75〜84／85歳以上）が確定。**第1号＋第2号＝全体を20期すべてで検算済み</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3400,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>令和7年度 調査結果報告書（令和8年3月・104頁）</t>
+          <t>認定審査・更新認定の運用変更の有無</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
@@ -3401,19 +3408,19 @@
           <t>町</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>完了</t>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>―</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>**単純集計とリスク分析（年齢階層別・男女別・認定状況別）を取得。**集計結果・分析報告書として取りまとめ済み。設計25件のうち4件が掲載済み、17件が個票を要し、4件は設問が存在しない</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
@@ -3425,7 +3432,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>令和7年度調査の**個票データ**</t>
+          <t>令和3〜8年度 サービス別給付費・利用者数</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
@@ -3433,9 +3440,9 @@
           <t>町</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>要対応</t>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
@@ -3445,7 +3452,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>要介護度別・世帯構成別のクロス集計17件に必要。地区情報の有無も要確認（層化抽出に居住地区を用いている）</t>
+          <t>見える化との突合</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3464,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>令和7年度調査の調査票・配布数・回収数・実施時期</t>
+          <t>令和7年度 調査結果報告書（令和8年3月・104頁）</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
@@ -3465,19 +3472,19 @@
           <t>町</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>計画書第2章1(1)の記載と、前回調査との設問の異同の確認に必要</t>
+          <t>**単純集計とリスク分析（年齢階層別・男女別・認定状況別）を取得。**集計結果・分析報告書として取りまとめ済み。設計25件のうち4件が掲載済み、17件が個票を要し、4件は設問が存在しない</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3496,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>在宅介護実態調査の**配布方法**（ケアマネジャー経由か否か）</t>
+          <t>令和7年度調査の**個票データ**</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
@@ -3497,9 +3504,9 @@
           <t>町</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
@@ -3509,7 +3516,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>**ケアマネジャー経由の場合、サービス未利用者が構造的に対象外となり、認定と利用のギャップを検証できない。**補足調査の要否判断に直結</t>
+          <t>要介護度別・世帯構成別のクロス集計17件に必要。地区情報の有無も要確認（層化抽出に居住地区を用いている）</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3528,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高と取崩方針</t>
+          <t>令和7年度調査の調査票・配布数・回収数・実施時期</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
@@ -3541,7 +3548,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>保険料算定に必須</t>
+          <t>計画書第2章1(1)の記載と、前回調査との設問の異同の確認に必要</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3560,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>所得段階別第1号被保険者数</t>
+          <t>在宅介護実態調査の**配布方法**（ケアマネジャー経由か否か）</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -3573,7 +3580,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>**ケアマネジャー経由の場合、サービス未利用者が構造的に対象外となり、認定と利用のギャップを検証できない。**補足調査の要否判断に直結</t>
         </is>
       </c>
     </row>
@@ -3585,7 +3592,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>地域支援事業費の実績と事業別内訳</t>
+          <t>介護給付費準備基金の残高と取崩方針</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
@@ -3605,7 +3612,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>保険料算定に必須</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3624,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>総合事業・通いの場の事業実績（令和3〜7年度）</t>
+          <t>所得段階別第1号被保険者数</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
@@ -3637,7 +3644,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>見える化に令和3年度以降がないため代替が必要</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3656,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>事業所別定員・稼働率・町内外利用・待機・休廃止</t>
+          <t>地域支援事業費の実績と事業別内訳</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
@@ -3669,7 +3676,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>供給制約の確認</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3688,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>居宅介護支援事業所の担当件数・受付状況</t>
+          <t>総合事業・通いの場の事業実績（令和3〜7年度）</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
@@ -3701,7 +3708,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>事業所5→3の減少と在宅利用低下の関係</t>
+          <t>見える化に令和3年度以降がないため代替が必要</t>
         </is>
       </c>
     </row>
@@ -3713,12 +3720,12 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>認知症施策の実績（研修、初期集中支援チーム等）</t>
+          <t>事業所別定員・稼働率・町内外利用・待機・休廃止</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>町・県</t>
+          <t>町</t>
         </is>
       </c>
       <c r="D29" s="16" t="inlineStr">
@@ -3733,7 +3740,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>見える化では把握できない</t>
+          <t>供給制約の確認</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3752,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>障がい：令和6〜8年度 サービス別実績、支給決定量、町内外事業所別利用</t>
+          <t>居宅介護支援事業所の担当件数・受付状況</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
@@ -3765,7 +3772,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>見込量算定に必須</t>
+          <t>事業所5→3の減少と在宅利用低下の関係</t>
         </is>
       </c>
     </row>
@@ -3777,12 +3784,12 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>障がい：セルフプラン件数、相談支援専門員数</t>
+          <t>認知症施策の実績（研修、初期集中支援チーム等）</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>町・県</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
@@ -3797,7 +3804,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>国の新規成果目標「望まないセルフプランゼロ」の起点</t>
+          <t>見える化では把握できない</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3816,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>障がい：特別支援学校卒業予定者、医療的ケア児の状況</t>
+          <t>障がい：令和6〜8年度 サービス別実績、支給決定量、町内外事業所別利用</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
@@ -3829,24 +3836,24 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>18歳移行の見込量</t>
+          <t>見込量算定に必須</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>町資料</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>★0727版アンケート調査票（一般用・児童用）</t>
+          <t>障がい：セルフプラン件数、相談支援専門員数</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>町・他メンバー</t>
+          <t>町</t>
         </is>
       </c>
       <c r="D33" s="16" t="inlineStr">
@@ -3861,37 +3868,101 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>本文復元の対象ファイル。手元にない</t>
+          <t>国の新規成果目標「望まないセルフプランゼロ」の起点</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
+          <t>町資料</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>障がい：特別支援学校卒業予定者、医療的ケア児の状況</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>町</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>18歳移行の見込量</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>★0727版アンケート調査票（一般用・児童用）</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>町・他メンバー</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>本文復元の対象ファイル。手元にない</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>打合せ記録（契約後）</t>
         </is>
       </c>
-      <c r="C34" s="13" t="inlineStr">
+      <c r="C36" s="13" t="inlineStr">
         <is>
           <t>受託者作成・町確認</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="E34" s="13" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>仕様書8①により受託者が作成し相互確認する義務</t>
         </is>
